--- a/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9426_escuela-llano-subercaseaux_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{706B5740-34C3-4E14-9FAC-6484569D0C6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50FA336F-D253-49C7-9FFC-9FDE373B9881}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{60EB9428-8B98-45DB-AB2D-170DFED9751B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AC3B2ED-FC0C-4A65-A899-BF8024AE74D7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DFE629B-B06F-422F-967B-FFB6EA6DC30A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84A45861-C7B0-4CC2-A975-D39F9DC84280}"/>
 </file>